--- a/tools/importer/reports/import-semaglutide-content-page.report.xlsx
+++ b/tools/importer/reports/import-semaglutide-content-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>semaglutide-content-page</t>
   </si>
   <si>
-    <t>2026-04-16T10:33:44.737Z</t>
+    <t>2026-04-16T16:18:30.858Z</t>
   </si>
   <si>
     <t>Novo Nordisk medicines containing semaglutide | semaglutide.com</t>
@@ -70,7 +70,7 @@
     <t>semaglutide/patient-safety</t>
   </si>
   <si>
-    <t>2026-04-16T10:33:38.078Z</t>
+    <t>2026-04-16T16:18:25.214Z</t>
   </si>
   <si>
     <t>Semaglutide Patient Safety Updates | semaglutide.com</t>
